--- a/Data/Excel/item.xlsx
+++ b/Data/Excel/item.xlsx
@@ -495,7 +495,7 @@
         <x:v>Assets/Arts/UI/Icons/Item/Gold.png</x:v>
       </x:c>
       <x:c r="H5" s="18" t="str">
-        <x:v>Arts/Drops/GoldDrop</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I5" s="19" t="b">
         <x:v>1</x:v>
@@ -531,7 +531,7 @@
         <x:v>Assets/Arts/UI/Icons/Item/BombTree.png</x:v>
       </x:c>
       <x:c r="H6" s="18" t="str">
-        <x:v>Arts/Drops/BombTreeDrop</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I6" s="19" t="b">
         <x:v>0</x:v>
@@ -567,7 +567,7 @@
         <x:v>Assets/Arts/UI/Icons/Item/BombBridge.png</x:v>
       </x:c>
       <x:c r="H7" s="18" t="str">
-        <x:v>Arts/Drops/BombBridgeDrop</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I7" s="19" t="b">
         <x:v>0</x:v>
@@ -603,7 +603,7 @@
         <x:v>Assets/Arts/UI/Icons/Item/BlueprintArrow.png</x:v>
       </x:c>
       <x:c r="H8" s="18" t="str">
-        <x:v>Arts/Drops/BlueprintDrop</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I8" s="19" t="b">
         <x:v>1</x:v>
@@ -639,7 +639,7 @@
         <x:v>Assets/Arts/UI/Icons/Item/Seed.png</x:v>
       </x:c>
       <x:c r="H9" s="18" t="str">
-        <x:v>Arts/Drops/SeedDrop</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I9" s="19" t="b">
         <x:v>1</x:v>
@@ -675,7 +675,7 @@
         <x:v>Assets/Arts/UI/Icons/Item/SlimeCore.png</x:v>
       </x:c>
       <x:c r="H10" s="18" t="str">
-        <x:v>Arts/Drops/SlimeCoreDrop</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I10" s="19" t="b">
         <x:v>1</x:v>

--- a/Data/Excel/item.xlsx
+++ b/Data/Excel/item.xlsx
@@ -513,7 +513,7 @@
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="18" t="str"/>
       <x:c r="B6" s="18" t="n">
-        <x:v>101</x:v>
+        <x:v>1000101</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
         <x:v>伐木炸弹</x:v>
@@ -549,7 +549,7 @@
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="18" t="str"/>
       <x:c r="B7" s="18" t="n">
-        <x:v>102</x:v>
+        <x:v>1000102</x:v>
       </x:c>
       <x:c r="C7" s="18" t="str">
         <x:v>拆桥工具</x:v>
@@ -585,7 +585,7 @@
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="18" t="str"/>
       <x:c r="B8" s="18" t="n">
-        <x:v>201</x:v>
+        <x:v>3000201</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
         <x:v>箭塔图纸</x:v>
@@ -621,7 +621,7 @@
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="18" t="str"/>
       <x:c r="B9" s="18" t="n">
-        <x:v>301</x:v>
+        <x:v>5000301</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
         <x:v>海岛种子</x:v>
@@ -657,7 +657,7 @@
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="18" t="str"/>
       <x:c r="B10" s="18" t="n">
-        <x:v>401</x:v>
+        <x:v>4000401</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
         <x:v>黏液核心</x:v>

--- a/Data/Excel/item.xlsx
+++ b/Data/Excel/item.xlsx
@@ -185,7 +185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,16 +438,16 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>1</v>
+        <v>20000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="E5">
@@ -458,7 +458,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Gold.png</t>
+          <t>Assets/Arts/UI/Icons/Item/Wood.png</t>
         </is>
       </c>
       <c r="I5">
@@ -476,16 +476,16 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>2</v>
+        <v>20000002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="E6">
@@ -496,7 +496,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Wood.png</t>
+          <t>Assets/Arts/UI/Icons/Item/Stone.png</t>
         </is>
       </c>
       <c r="I6">
@@ -514,16 +514,16 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>3</v>
+        <v>20000003</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E7">
@@ -534,7 +534,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Stone.png</t>
+          <t>Assets/Arts/UI/Icons/Item/Gold.png</t>
         </is>
       </c>
       <c r="I7">
@@ -552,16 +552,16 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>4</v>
+        <v>20000004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Copper Ore</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Copper Ore</t>
         </is>
       </c>
       <c r="E8">
@@ -572,7 +572,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Food.png</t>
+          <t>Assets/Arts/UI/Icons/Item/CopperOre.png</t>
         </is>
       </c>
       <c r="I8">
@@ -590,16 +590,16 @@
     </row>
     <row r="9">
       <c r="B9">
-        <v>5</v>
+        <v>20000005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Copper Ore</t>
+          <t>Iron Ore</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Copper Ore</t>
+          <t>Iron Ore</t>
         </is>
       </c>
       <c r="E9">
@@ -610,7 +610,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/CopperOre.png</t>
+          <t>Assets/Arts/UI/Icons/Item/IronOre.png</t>
         </is>
       </c>
       <c r="I9">
@@ -628,16 +628,16 @@
     </row>
     <row r="10">
       <c r="B10">
-        <v>6</v>
+        <v>20100001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iron Ore</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Iron Ore</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E10">
@@ -648,7 +648,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/IronOre.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/wheat.png</t>
         </is>
       </c>
       <c r="I10">
@@ -666,16 +666,16 @@
     </row>
     <row r="11">
       <c r="B11">
-        <v>7</v>
+        <v>20100002</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Herb</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Herb</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="E11">
@@ -686,7 +686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Herb.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/tomato.png</t>
         </is>
       </c>
       <c r="I11">
@@ -704,16 +704,16 @@
     </row>
     <row r="12">
       <c r="B12">
-        <v>8</v>
+        <v>20100003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Herb</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Herb</t>
         </is>
       </c>
       <c r="E12">
@@ -724,7 +724,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Wheat.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/aloe.png</t>
         </is>
       </c>
       <c r="I12">
@@ -742,16 +742,16 @@
     </row>
     <row r="13">
       <c r="B13">
-        <v>9</v>
+        <v>20100004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Flower</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Flower</t>
         </is>
       </c>
       <c r="E13">
@@ -762,7 +762,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Tomato.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/mint.png</t>
         </is>
       </c>
       <c r="I13">
@@ -780,34 +780,34 @@
     </row>
     <row r="14">
       <c r="B14">
-        <v>10</v>
+        <v>20200001</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Flower</t>
+          <t>Wheat Seed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Flower</t>
+          <t>Wheat seed</t>
         </is>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Flower.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/wheat.png</t>
         </is>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14">
-        <v>999999</v>
+        <v>999</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -818,34 +818,34 @@
     </row>
     <row r="15">
       <c r="B15">
-        <v>1000101</v>
+        <v>20200002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bomb Tree</t>
+          <t>Tomato Seed</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Destroy tree obstacle</t>
+          <t>Tomato seed</t>
         </is>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/BombTree.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/tomato.png</t>
         </is>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -856,34 +856,34 @@
     </row>
     <row r="16">
       <c r="B16">
-        <v>1000102</v>
+        <v>20200003</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bomb Bridge</t>
+          <t>Herb Seed</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Destroy bridge obstacle</t>
+          <t>Herb seed</t>
         </is>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/BombBridge.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/aloe.png</t>
         </is>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -894,27 +894,27 @@
     </row>
     <row r="17">
       <c r="B17">
-        <v>3000201</v>
+        <v>20200004</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Blueprint</t>
+          <t>Flower Seed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Building blueprint</t>
+          <t>Flower seed</t>
         </is>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Blueprint.png</t>
+          <t>Assets/Arts/UI/Icons/System/crop/mint.png</t>
         </is>
       </c>
       <c r="I17">
@@ -932,34 +932,34 @@
     </row>
     <row r="18">
       <c r="B18">
-        <v>4000401</v>
+        <v>20300001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slime Core</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Monster material</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/SlimeCore.png</t>
+          <t>Assets/Arts/UI/Icons/Item/Food.png</t>
         </is>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="J18">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -970,39 +970,495 @@
     </row>
     <row r="19">
       <c r="B19">
-        <v>5000301</v>
+        <v>20300002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Plank</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Basic seed</t>
+          <t>Plank</t>
         </is>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Assets/Arts/UI/Icons/Item/Seed.png</t>
+          <t>Assets/Arts/UI/Icons/Item/Plank.png</t>
         </is>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
+        <v>999999</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20">
+        <v>20300003</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Copper Ingot</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Copper Ingot</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/CopperIngot.png</t>
+        </is>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>999999</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21">
+        <v>20300004</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Iron Ingot</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Iron Ingot</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/IronIngot.png</t>
+        </is>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>999999</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22">
+        <v>20400001</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bomb Tree</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Destroy tree obstacle</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BombTree.png</t>
+        </is>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>99</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23">
+        <v>20400002</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bomb Bridge</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Destroy bridge obstacle</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BombBridge.png</t>
+        </is>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>99</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24">
+        <v>20500001</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Blueprint</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Building blueprint</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/Blueprint.png</t>
+        </is>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
         <v>999</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25">
+        <v>20600001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Slime Core</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Monster material</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/SlimeCore.png</t>
+        </is>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>999</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26">
+        <v>20700001</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Basic Axe</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Basic tool for chopping trees.</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BasicAxe.png</t>
+        </is>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27">
+        <v>20700002</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Basic Pickaxe</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Basic tool for mining stone and ore.</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BasicPickaxe.png</t>
+        </is>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28">
+        <v>20700003</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Basic Hoe</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Basic tool for cultivating farmland.</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BasicHoe.png</t>
+        </is>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29">
+        <v>20700004</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Basic Watering Can</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Basic tool for watering crops.</t>
+        </is>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BasicWateringCan.png</t>
+        </is>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30">
+        <v>20700005</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Basic Fishing Rod</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Basic tool for fishing.</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BasicFishingRod.png</t>
+        </is>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31">
+        <v>20700006</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Basic Hammer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Basic tool for building and repairing.</t>
+        </is>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Assets/Arts/UI/Icons/Item/BasicHammer.png</t>
+        </is>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
         <v>0</v>
       </c>
     </row>
